--- a/reports/20260803-20260809/熊猫密室周报截图核对底表_20260803-20260809.xlsx
+++ b/reports/20260803-20260809/熊猫密室周报截图核对底表_20260803-20260809.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="1" r:id="R6e93782a39e54bc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域截图锁定" sheetId="2" r:id="R78e9e5dfc1244448"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工销售金额排名" sheetId="3" r:id="R9f6f93a8f55d4460"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工办卡率排名" sheetId="4" r:id="Rfba35ddefe5a4ce3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工续卡排名" sheetId="5" r:id="Rbb7c65ca7adb48e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="6" r:id="R0fb7331e7bee4bec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="1" r:id="R622ca084c6884e1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域截图锁定" sheetId="2" r:id="R78b70b330df84cca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工销售金额排名" sheetId="3" r:id="Raeb7c0dc8ecd45a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工办卡率排名" sheetId="4" r:id="Rdb88c87cfe67455a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工续卡排名" sheetId="5" r:id="R72500682615e45bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="6" r:id="R2354a0ba6f3c43de"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2667,10 +2667,10 @@
         <x:v>武汉武昌万象城</x:v>
       </x:c>
       <x:c r="C21" s="15" t="str">
-        <x:v>待补</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="str">
-        <x:v>待补</x:v>
+        <x:v>A类</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="n">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E21" s="16" t="n">
         <x:v>11480</x:v>
@@ -2769,10 +2769,10 @@
         <x:v>郑州美盛天街</x:v>
       </x:c>
       <x:c r="C22" s="20" t="str">
-        <x:v>待补</x:v>
-      </x:c>
-      <x:c r="D22" s="20" t="str">
-        <x:v>待补</x:v>
+        <x:v>B类</x:v>
+      </x:c>
+      <x:c r="D22" s="20" t="n">
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E22" s="21" t="n">
         <x:v>24386.01</x:v>
@@ -2866,7 +2866,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5bd5236cf344796"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6a141090dd24c74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3382,10 +3382,12 @@
       <x:c r="E8" s="16" t="n">
         <x:v>13806</x:v>
       </x:c>
-      <x:c r="F8" s="16"/>
+      <x:c r="F8" s="16" t="n">
+        <x:v>9173.2</x:v>
+      </x:c>
       <x:c r="G8" s="16" t="n">
         <x:f>IFERROR(E8-F8,0)</x:f>
-        <x:v>13806</x:v>
+        <x:v>4632.799999999999</x:v>
       </x:c>
       <x:c r="H8" s="17" t="n">
         <x:v>0.9861</x:v>
@@ -3651,10 +3653,12 @@
       <x:c r="E15" s="16" t="n">
         <x:v>11526.75</x:v>
       </x:c>
-      <x:c r="F15" s="16"/>
+      <x:c r="F15" s="16" t="n">
+        <x:v>11015.9</x:v>
+      </x:c>
       <x:c r="G15" s="16" t="n">
         <x:f>IFERROR(E15-F15,0)</x:f>
-        <x:v>11526.75</x:v>
+        <x:v>510.85000000000036</x:v>
       </x:c>
       <x:c r="H15" s="17" t="n">
         <x:v>0.7736</x:v>
@@ -3688,10 +3692,12 @@
       <x:c r="E16" s="16" t="n">
         <x:v>11207.05</x:v>
       </x:c>
-      <x:c r="F16" s="16"/>
+      <x:c r="F16" s="16" t="n">
+        <x:v>11152.2</x:v>
+      </x:c>
       <x:c r="G16" s="16" t="n">
         <x:f>IFERROR(E16-F16,0)</x:f>
-        <x:v>11207.05</x:v>
+        <x:v>54.849999999998545</x:v>
       </x:c>
       <x:c r="H16" s="17" t="n">
         <x:v>1.4009</x:v>
@@ -3841,11 +3847,11 @@
         <x:v>9070</x:v>
       </x:c>
       <x:c r="F20" s="16" t="n">
-        <x:v>12510</x:v>
+        <x:v>12664</x:v>
       </x:c>
       <x:c r="G20" s="16" t="n">
         <x:f>IFERROR(E20-F20,0)</x:f>
-        <x:v>-3440</x:v>
+        <x:v>-3594</x:v>
       </x:c>
       <x:c r="H20" s="17" t="n">
         <x:v>0.7315</x:v>
@@ -3879,10 +3885,12 @@
       <x:c r="E21" s="16" t="n">
         <x:v>8711</x:v>
       </x:c>
-      <x:c r="F21" s="16"/>
+      <x:c r="F21" s="16" t="n">
+        <x:v>5748</x:v>
+      </x:c>
       <x:c r="G21" s="16" t="n">
         <x:f>IFERROR(E21-F21,0)</x:f>
-        <x:v>8711</x:v>
+        <x:v>2963</x:v>
       </x:c>
       <x:c r="H21" s="17" t="n">
         <x:v>0.7918999999999999</x:v>
@@ -3994,10 +4002,12 @@
       <x:c r="E24" s="16" t="n">
         <x:v>7654.2</x:v>
       </x:c>
-      <x:c r="F24" s="16"/>
+      <x:c r="F24" s="16" t="n">
+        <x:v>9131</x:v>
+      </x:c>
       <x:c r="G24" s="16" t="n">
         <x:f>IFERROR(E24-F24,0)</x:f>
-        <x:v>7654.2</x:v>
+        <x:v>-1476.8000000000002</x:v>
       </x:c>
       <x:c r="H24" s="17" t="n">
         <x:v>0.6968000000000001</x:v>
@@ -4226,10 +4236,12 @@
       <x:c r="E30" s="16" t="n">
         <x:v>5764</x:v>
       </x:c>
-      <x:c r="F30" s="16"/>
+      <x:c r="F30" s="16" t="n">
+        <x:v>2129</x:v>
+      </x:c>
       <x:c r="G30" s="16" t="n">
         <x:f>IFERROR(E30-F30,0)</x:f>
-        <x:v>5764</x:v>
+        <x:v>3635</x:v>
       </x:c>
       <x:c r="H30" s="17" t="n">
         <x:v>0.5703</x:v>
@@ -4263,10 +4275,12 @@
       <x:c r="E31" s="16" t="n">
         <x:v>5485</x:v>
       </x:c>
-      <x:c r="F31" s="16"/>
+      <x:c r="F31" s="16" t="n">
+        <x:v>6139</x:v>
+      </x:c>
       <x:c r="G31" s="16" t="n">
         <x:f>IFERROR(E31-F31,0)</x:f>
-        <x:v>5485</x:v>
+        <x:v>-654</x:v>
       </x:c>
       <x:c r="H31" s="17" t="n">
         <x:v>0.7031999999999999</x:v>
@@ -4339,10 +4353,12 @@
       <x:c r="E33" s="16" t="n">
         <x:v>5409</x:v>
       </x:c>
-      <x:c r="F33" s="16"/>
+      <x:c r="F33" s="16" t="n">
+        <x:v>5395</x:v>
+      </x:c>
       <x:c r="G33" s="16" t="n">
         <x:f>IFERROR(E33-F33,0)</x:f>
-        <x:v>5409</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H33" s="17" t="n">
         <x:v>0.5212</x:v>
@@ -4415,10 +4431,12 @@
       <x:c r="E35" s="16" t="n">
         <x:v>5207</x:v>
       </x:c>
-      <x:c r="F35" s="16"/>
+      <x:c r="F35" s="16" t="n">
+        <x:v>1555</x:v>
+      </x:c>
       <x:c r="G35" s="16" t="n">
         <x:f>IFERROR(E35-F35,0)</x:f>
-        <x:v>5207</x:v>
+        <x:v>3652</x:v>
       </x:c>
       <x:c r="H35" s="17" t="n">
         <x:v>0.4775</x:v>
@@ -4452,10 +4470,12 @@
       <x:c r="E36" s="16" t="n">
         <x:v>5099</x:v>
       </x:c>
-      <x:c r="F36" s="16"/>
+      <x:c r="F36" s="16" t="n">
+        <x:v>5199</x:v>
+      </x:c>
       <x:c r="G36" s="16" t="n">
         <x:f>IFERROR(E36-F36,0)</x:f>
-        <x:v>5099</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="H36" s="17" t="n">
         <x:v>0.7214</x:v>
@@ -4604,10 +4624,12 @@
       <x:c r="E40" s="16" t="n">
         <x:v>4581</x:v>
       </x:c>
-      <x:c r="F40" s="16"/>
+      <x:c r="F40" s="16" t="n">
+        <x:v>2911</x:v>
+      </x:c>
       <x:c r="G40" s="16" t="n">
         <x:f>IFERROR(E40-F40,0)</x:f>
-        <x:v>4581</x:v>
+        <x:v>1670</x:v>
       </x:c>
       <x:c r="H40" s="17" t="n">
         <x:v>0.8521</x:v>
@@ -4680,10 +4702,12 @@
       <x:c r="E42" s="16" t="n">
         <x:v>4264</x:v>
       </x:c>
-      <x:c r="F42" s="16"/>
+      <x:c r="F42" s="16" t="n">
+        <x:v>3647</x:v>
+      </x:c>
       <x:c r="G42" s="16" t="n">
         <x:f>IFERROR(E42-F42,0)</x:f>
-        <x:v>4264</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="H42" s="17" t="n">
         <x:v>0.5134000000000001</x:v>
@@ -4754,10 +4778,12 @@
       <x:c r="E44" s="16" t="n">
         <x:v>3554</x:v>
       </x:c>
-      <x:c r="F44" s="16"/>
+      <x:c r="F44" s="16" t="n">
+        <x:v>4558.2</x:v>
+      </x:c>
       <x:c r="G44" s="16" t="n">
         <x:f>IFERROR(E44-F44,0)</x:f>
-        <x:v>3554</x:v>
+        <x:v>-1004.1999999999998</x:v>
       </x:c>
       <x:c r="H44" s="17" t="n">
         <x:v>0.581</x:v>
@@ -4791,10 +4817,12 @@
       <x:c r="E45" s="16" t="n">
         <x:v>3477</x:v>
       </x:c>
-      <x:c r="F45" s="16"/>
+      <x:c r="F45" s="16" t="n">
+        <x:v>1879</x:v>
+      </x:c>
       <x:c r="G45" s="16" t="n">
         <x:f>IFERROR(E45-F45,0)</x:f>
-        <x:v>3477</x:v>
+        <x:v>1598</x:v>
       </x:c>
       <x:c r="H45" s="17" t="n">
         <x:v>0.4439</x:v>
@@ -4828,10 +4856,12 @@
       <x:c r="E46" s="16" t="n">
         <x:v>3213.9</x:v>
       </x:c>
-      <x:c r="F46" s="16"/>
+      <x:c r="F46" s="16" t="n">
+        <x:v>6187</x:v>
+      </x:c>
       <x:c r="G46" s="16" t="n">
         <x:f>IFERROR(E46-F46,0)</x:f>
-        <x:v>3213.9</x:v>
+        <x:v>-2973.1</x:v>
       </x:c>
       <x:c r="H46" s="17" t="n">
         <x:v>0.45270000000000005</x:v>
@@ -4902,10 +4932,12 @@
       <x:c r="E48" s="16" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="F48" s="16"/>
+      <x:c r="F48" s="16" t="n">
+        <x:v>5506</x:v>
+      </x:c>
       <x:c r="G48" s="16" t="n">
         <x:f>IFERROR(E48-F48,0)</x:f>
-        <x:v>3000</x:v>
+        <x:v>-2506</x:v>
       </x:c>
       <x:c r="H48" s="17" t="n">
         <x:v>0.14679999999999999</x:v>
@@ -5015,10 +5047,12 @@
       <x:c r="E51" s="16" t="n">
         <x:v>2738</x:v>
       </x:c>
-      <x:c r="F51" s="16"/>
+      <x:c r="F51" s="16" t="n">
+        <x:v>3880</x:v>
+      </x:c>
       <x:c r="G51" s="16" t="n">
         <x:f>IFERROR(E51-F51,0)</x:f>
-        <x:v>2738</x:v>
+        <x:v>-1142</x:v>
       </x:c>
       <x:c r="H51" s="17" t="n">
         <x:v>0.6084</x:v>
@@ -5052,10 +5086,12 @@
       <x:c r="E52" s="16" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="F52" s="16"/>
+      <x:c r="F52" s="16" t="n">
+        <x:v>2236</x:v>
+      </x:c>
       <x:c r="G52" s="16" t="n">
         <x:f>IFERROR(E52-F52,0)</x:f>
-        <x:v>2550</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="H52" s="17" t="n">
         <x:v>0.3333</x:v>
@@ -5090,11 +5126,11 @@
         <x:v>2494</x:v>
       </x:c>
       <x:c r="F53" s="16" t="n">
-        <x:v>4814</x:v>
+        <x:v>4615</x:v>
       </x:c>
       <x:c r="G53" s="16" t="n">
         <x:f>IFERROR(E53-F53,0)</x:f>
-        <x:v>-2320</x:v>
+        <x:v>-2121</x:v>
       </x:c>
       <x:c r="H53" s="17" t="n">
         <x:v>0.3563</x:v>
@@ -5128,10 +5164,12 @@
       <x:c r="E54" s="16" t="n">
         <x:v>2473.2</x:v>
       </x:c>
-      <x:c r="F54" s="16"/>
+      <x:c r="F54" s="16" t="n">
+        <x:v>756</x:v>
+      </x:c>
       <x:c r="G54" s="16" t="n">
         <x:f>IFERROR(E54-F54,0)</x:f>
-        <x:v>2473.2</x:v>
+        <x:v>1717.1999999999998</x:v>
       </x:c>
       <x:c r="H54" s="17" t="n">
         <x:v>0.32049999999999995</x:v>
@@ -5280,10 +5318,12 @@
       <x:c r="E58" s="16" t="n">
         <x:v>2226.1</x:v>
       </x:c>
-      <x:c r="F58" s="16"/>
+      <x:c r="F58" s="16" t="n">
+        <x:v>4214.15</x:v>
+      </x:c>
       <x:c r="G58" s="16" t="n">
         <x:f>IFERROR(E58-F58,0)</x:f>
-        <x:v>2226.1</x:v>
+        <x:v>-1988.0499999999997</x:v>
       </x:c>
       <x:c r="H58" s="17" t="n">
         <x:v>0.3153</x:v>
@@ -5318,11 +5358,11 @@
         <x:v>1660</x:v>
       </x:c>
       <x:c r="F59" s="16" t="n">
-        <x:v>6319</x:v>
+        <x:v>5835</x:v>
       </x:c>
       <x:c r="G59" s="16" t="n">
         <x:f>IFERROR(E59-F59,0)</x:f>
-        <x:v>-4659</x:v>
+        <x:v>-4175</x:v>
       </x:c>
       <x:c r="H59" s="17" t="n">
         <x:v>0.664</x:v>
@@ -5395,10 +5435,12 @@
       <x:c r="E61" s="16" t="n">
         <x:v>1085</x:v>
       </x:c>
-      <x:c r="F61" s="16"/>
+      <x:c r="F61" s="16" t="n">
+        <x:v>484</x:v>
+      </x:c>
       <x:c r="G61" s="16" t="n">
         <x:f>IFERROR(E61-F61,0)</x:f>
-        <x:v>1085</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="H61" s="17" t="n">
         <x:v>0.2893</x:v>
@@ -5508,10 +5550,12 @@
       <x:c r="E64" s="16" t="n">
         <x:v>895</x:v>
       </x:c>
-      <x:c r="F64" s="16"/>
+      <x:c r="F64" s="16" t="n">
+        <x:v>1524</x:v>
+      </x:c>
       <x:c r="G64" s="16" t="n">
         <x:f>IFERROR(E64-F64,0)</x:f>
-        <x:v>895</x:v>
+        <x:v>-629</x:v>
       </x:c>
       <x:c r="H64" s="17" t="n">
         <x:v>0</x:v>
@@ -5645,7 +5689,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69e39b48d3944856"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3613ad92dddd4aa7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5722,10 +5766,12 @@
       <x:c r="E2" s="16" t="n">
         <x:v>5409</x:v>
       </x:c>
-      <x:c r="F2" s="16"/>
+      <x:c r="F2" s="16" t="n">
+        <x:v>5395</x:v>
+      </x:c>
       <x:c r="G2" s="16" t="n">
         <x:f>IFERROR(E2-F2,0)</x:f>
-        <x:v>5409</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="17" t="n">
         <x:v>0.5212</x:v>
@@ -5759,10 +5805,12 @@
       <x:c r="E3" s="16" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="F3" s="16"/>
+      <x:c r="F3" s="16" t="n">
+        <x:v>5506</x:v>
+      </x:c>
       <x:c r="G3" s="16" t="n">
         <x:f>IFERROR(E3-F3,0)</x:f>
-        <x:v>3000</x:v>
+        <x:v>-2506</x:v>
       </x:c>
       <x:c r="H3" s="17" t="n">
         <x:v>0.14679999999999999</x:v>
@@ -5870,10 +5918,12 @@
       <x:c r="E6" s="16" t="n">
         <x:v>1085</x:v>
       </x:c>
-      <x:c r="F6" s="16"/>
+      <x:c r="F6" s="16" t="n">
+        <x:v>484</x:v>
+      </x:c>
       <x:c r="G6" s="16" t="n">
         <x:f>IFERROR(E6-F6,0)</x:f>
-        <x:v>1085</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="H6" s="17" t="n">
         <x:v>0.2893</x:v>
@@ -6018,10 +6068,12 @@
       <x:c r="E10" s="16" t="n">
         <x:v>2226.1</x:v>
       </x:c>
-      <x:c r="F10" s="16"/>
+      <x:c r="F10" s="16" t="n">
+        <x:v>4214.15</x:v>
+      </x:c>
       <x:c r="G10" s="16" t="n">
         <x:f>IFERROR(E10-F10,0)</x:f>
-        <x:v>2226.1</x:v>
+        <x:v>-1988.0499999999997</x:v>
       </x:c>
       <x:c r="H10" s="17" t="n">
         <x:v>0.3153</x:v>
@@ -6055,10 +6107,12 @@
       <x:c r="E11" s="16" t="n">
         <x:v>8711</x:v>
       </x:c>
-      <x:c r="F11" s="16"/>
+      <x:c r="F11" s="16" t="n">
+        <x:v>5748</x:v>
+      </x:c>
       <x:c r="G11" s="16" t="n">
         <x:f>IFERROR(E11-F11,0)</x:f>
-        <x:v>8711</x:v>
+        <x:v>2963</x:v>
       </x:c>
       <x:c r="H11" s="17" t="n">
         <x:v>0.7918999999999999</x:v>
@@ -6093,11 +6147,11 @@
         <x:v>9070</x:v>
       </x:c>
       <x:c r="F12" s="16" t="n">
-        <x:v>12510</x:v>
+        <x:v>12664</x:v>
       </x:c>
       <x:c r="G12" s="16" t="n">
         <x:f>IFERROR(E12-F12,0)</x:f>
-        <x:v>-3440</x:v>
+        <x:v>-3594</x:v>
       </x:c>
       <x:c r="H12" s="17" t="n">
         <x:v>0.7315</x:v>
@@ -6131,10 +6185,12 @@
       <x:c r="E13" s="16" t="n">
         <x:v>5207</x:v>
       </x:c>
-      <x:c r="F13" s="16"/>
+      <x:c r="F13" s="16" t="n">
+        <x:v>1555</x:v>
+      </x:c>
       <x:c r="G13" s="16" t="n">
         <x:f>IFERROR(E13-F13,0)</x:f>
-        <x:v>5207</x:v>
+        <x:v>3652</x:v>
       </x:c>
       <x:c r="H13" s="17" t="n">
         <x:v>0.4775</x:v>
@@ -6324,10 +6380,12 @@
       <x:c r="E18" s="16" t="n">
         <x:v>4581</x:v>
       </x:c>
-      <x:c r="F18" s="16"/>
+      <x:c r="F18" s="16" t="n">
+        <x:v>2911</x:v>
+      </x:c>
       <x:c r="G18" s="16" t="n">
         <x:f>IFERROR(E18-F18,0)</x:f>
-        <x:v>4581</x:v>
+        <x:v>1670</x:v>
       </x:c>
       <x:c r="H18" s="17" t="n">
         <x:v>0.8521</x:v>
@@ -6361,10 +6419,12 @@
       <x:c r="E19" s="16" t="n">
         <x:v>2738</x:v>
       </x:c>
-      <x:c r="F19" s="16"/>
+      <x:c r="F19" s="16" t="n">
+        <x:v>3880</x:v>
+      </x:c>
       <x:c r="G19" s="16" t="n">
         <x:f>IFERROR(E19-F19,0)</x:f>
-        <x:v>2738</x:v>
+        <x:v>-1142</x:v>
       </x:c>
       <x:c r="H19" s="17" t="n">
         <x:v>0.6084</x:v>
@@ -6437,10 +6497,12 @@
       <x:c r="E21" s="16" t="n">
         <x:v>5764</x:v>
       </x:c>
-      <x:c r="F21" s="16"/>
+      <x:c r="F21" s="16" t="n">
+        <x:v>2129</x:v>
+      </x:c>
       <x:c r="G21" s="16" t="n">
         <x:f>IFERROR(E21-F21,0)</x:f>
-        <x:v>5764</x:v>
+        <x:v>3635</x:v>
       </x:c>
       <x:c r="H21" s="17" t="n">
         <x:v>0.5703</x:v>
@@ -6474,10 +6536,12 @@
       <x:c r="E22" s="16" t="n">
         <x:v>5485</x:v>
       </x:c>
-      <x:c r="F22" s="16"/>
+      <x:c r="F22" s="16" t="n">
+        <x:v>6139</x:v>
+      </x:c>
       <x:c r="G22" s="16" t="n">
         <x:f>IFERROR(E22-F22,0)</x:f>
-        <x:v>5485</x:v>
+        <x:v>-654</x:v>
       </x:c>
       <x:c r="H22" s="17" t="n">
         <x:v>0.7031999999999999</x:v>
@@ -6626,10 +6690,12 @@
       <x:c r="E26" s="16" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="F26" s="16"/>
+      <x:c r="F26" s="16" t="n">
+        <x:v>2236</x:v>
+      </x:c>
       <x:c r="G26" s="16" t="n">
         <x:f>IFERROR(E26-F26,0)</x:f>
-        <x:v>2550</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="H26" s="17" t="n">
         <x:v>0.3333</x:v>
@@ -6664,11 +6730,11 @@
         <x:v>2494</x:v>
       </x:c>
       <x:c r="F27" s="16" t="n">
-        <x:v>4814</x:v>
+        <x:v>4615</x:v>
       </x:c>
       <x:c r="G27" s="16" t="n">
         <x:f>IFERROR(E27-F27,0)</x:f>
-        <x:v>-2320</x:v>
+        <x:v>-2121</x:v>
       </x:c>
       <x:c r="H27" s="17" t="n">
         <x:v>0.3563</x:v>
@@ -6973,10 +7039,12 @@
       <x:c r="E35" s="16" t="n">
         <x:v>7654.2</x:v>
       </x:c>
-      <x:c r="F35" s="16"/>
+      <x:c r="F35" s="16" t="n">
+        <x:v>9131</x:v>
+      </x:c>
       <x:c r="G35" s="16" t="n">
         <x:f>IFERROR(E35-F35,0)</x:f>
-        <x:v>7654.2</x:v>
+        <x:v>-1476.8000000000002</x:v>
       </x:c>
       <x:c r="H35" s="17" t="n">
         <x:v>0.6968000000000001</x:v>
@@ -7127,10 +7195,12 @@
       <x:c r="E39" s="16" t="n">
         <x:v>11207.05</x:v>
       </x:c>
-      <x:c r="F39" s="16"/>
+      <x:c r="F39" s="16" t="n">
+        <x:v>11152.2</x:v>
+      </x:c>
       <x:c r="G39" s="16" t="n">
         <x:f>IFERROR(E39-F39,0)</x:f>
-        <x:v>11207.05</x:v>
+        <x:v>54.849999999998545</x:v>
       </x:c>
       <x:c r="H39" s="17" t="n">
         <x:v>1.4009</x:v>
@@ -7318,10 +7388,12 @@
       <x:c r="E44" s="16" t="n">
         <x:v>4264</x:v>
       </x:c>
-      <x:c r="F44" s="16"/>
+      <x:c r="F44" s="16" t="n">
+        <x:v>3647</x:v>
+      </x:c>
       <x:c r="G44" s="16" t="n">
         <x:f>IFERROR(E44-F44,0)</x:f>
-        <x:v>4264</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="H44" s="17" t="n">
         <x:v>0.5134000000000001</x:v>
@@ -7355,10 +7427,12 @@
       <x:c r="E45" s="16" t="n">
         <x:v>11526.75</x:v>
       </x:c>
-      <x:c r="F45" s="16"/>
+      <x:c r="F45" s="16" t="n">
+        <x:v>11015.9</x:v>
+      </x:c>
       <x:c r="G45" s="16" t="n">
         <x:f>IFERROR(E45-F45,0)</x:f>
-        <x:v>11526.75</x:v>
+        <x:v>510.85000000000036</x:v>
       </x:c>
       <x:c r="H45" s="17" t="n">
         <x:v>0.7736</x:v>
@@ -7509,10 +7583,12 @@
       <x:c r="E49" s="16" t="n">
         <x:v>13806</x:v>
       </x:c>
-      <x:c r="F49" s="16"/>
+      <x:c r="F49" s="16" t="n">
+        <x:v>9173.2</x:v>
+      </x:c>
       <x:c r="G49" s="16" t="n">
         <x:f>IFERROR(E49-F49,0)</x:f>
-        <x:v>13806</x:v>
+        <x:v>4632.799999999999</x:v>
       </x:c>
       <x:c r="H49" s="17" t="n">
         <x:v>0.9861</x:v>
@@ -7661,10 +7737,12 @@
       <x:c r="E53" s="16" t="n">
         <x:v>3554</x:v>
       </x:c>
-      <x:c r="F53" s="16"/>
+      <x:c r="F53" s="16" t="n">
+        <x:v>4558.2</x:v>
+      </x:c>
       <x:c r="G53" s="16" t="n">
         <x:f>IFERROR(E53-F53,0)</x:f>
-        <x:v>3554</x:v>
+        <x:v>-1004.1999999999998</x:v>
       </x:c>
       <x:c r="H53" s="17" t="n">
         <x:v>0.581</x:v>
@@ -7737,10 +7815,12 @@
       <x:c r="E55" s="16" t="n">
         <x:v>3477</x:v>
       </x:c>
-      <x:c r="F55" s="16"/>
+      <x:c r="F55" s="16" t="n">
+        <x:v>1879</x:v>
+      </x:c>
       <x:c r="G55" s="16" t="n">
         <x:f>IFERROR(E55-F55,0)</x:f>
-        <x:v>3477</x:v>
+        <x:v>1598</x:v>
       </x:c>
       <x:c r="H55" s="17" t="n">
         <x:v>0.4439</x:v>
@@ -7774,10 +7854,12 @@
       <x:c r="E56" s="16" t="n">
         <x:v>3213.9</x:v>
       </x:c>
-      <x:c r="F56" s="16"/>
+      <x:c r="F56" s="16" t="n">
+        <x:v>6187</x:v>
+      </x:c>
       <x:c r="G56" s="16" t="n">
         <x:f>IFERROR(E56-F56,0)</x:f>
-        <x:v>3213.9</x:v>
+        <x:v>-2973.1</x:v>
       </x:c>
       <x:c r="H56" s="17" t="n">
         <x:v>0.45270000000000005</x:v>
@@ -7848,10 +7930,12 @@
       <x:c r="E58" s="16" t="n">
         <x:v>2473.2</x:v>
       </x:c>
-      <x:c r="F58" s="16"/>
+      <x:c r="F58" s="16" t="n">
+        <x:v>756</x:v>
+      </x:c>
       <x:c r="G58" s="16" t="n">
         <x:f>IFERROR(E58-F58,0)</x:f>
-        <x:v>2473.2</x:v>
+        <x:v>1717.1999999999998</x:v>
       </x:c>
       <x:c r="H58" s="17" t="n">
         <x:v>0.32049999999999995</x:v>
@@ -8041,10 +8125,12 @@
       <x:c r="E63" s="16" t="n">
         <x:v>5099</x:v>
       </x:c>
-      <x:c r="F63" s="16"/>
+      <x:c r="F63" s="16" t="n">
+        <x:v>5199</x:v>
+      </x:c>
       <x:c r="G63" s="16" t="n">
         <x:f>IFERROR(E63-F63,0)</x:f>
-        <x:v>5099</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="H63" s="17" t="n">
         <x:v>0.7214</x:v>
@@ -8117,10 +8203,12 @@
       <x:c r="E65" s="16" t="n">
         <x:v>895</x:v>
       </x:c>
-      <x:c r="F65" s="16"/>
+      <x:c r="F65" s="16" t="n">
+        <x:v>1524</x:v>
+      </x:c>
       <x:c r="G65" s="16" t="n">
         <x:f>IFERROR(E65-F65,0)</x:f>
-        <x:v>895</x:v>
+        <x:v>-629</x:v>
       </x:c>
       <x:c r="H65" s="17" t="n">
         <x:v>0</x:v>
@@ -8155,11 +8243,11 @@
         <x:v>1660</x:v>
       </x:c>
       <x:c r="F66" s="16" t="n">
-        <x:v>6319</x:v>
+        <x:v>5835</x:v>
       </x:c>
       <x:c r="G66" s="16" t="n">
         <x:f>IFERROR(E66-F66,0)</x:f>
-        <x:v>-4659</x:v>
+        <x:v>-4175</x:v>
       </x:c>
       <x:c r="H66" s="17" t="n">
         <x:v>0.664</x:v>
@@ -8219,7 +8307,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b3fa895e5f543fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2933fd55b6494cdd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8452,10 +8540,12 @@
       <x:c r="E6" s="16" t="n">
         <x:v>13806</x:v>
       </x:c>
-      <x:c r="F6" s="16"/>
+      <x:c r="F6" s="16" t="n">
+        <x:v>9173.2</x:v>
+      </x:c>
       <x:c r="G6" s="16" t="n">
         <x:f>IFERROR(E6-F6,0)</x:f>
-        <x:v>13806</x:v>
+        <x:v>4632.799999999999</x:v>
       </x:c>
       <x:c r="H6" s="17" t="n">
         <x:v>0.9861</x:v>
@@ -8528,10 +8618,12 @@
       <x:c r="E8" s="16" t="n">
         <x:v>8711</x:v>
       </x:c>
-      <x:c r="F8" s="16"/>
+      <x:c r="F8" s="16" t="n">
+        <x:v>5748</x:v>
+      </x:c>
       <x:c r="G8" s="16" t="n">
         <x:f>IFERROR(E8-F8,0)</x:f>
-        <x:v>8711</x:v>
+        <x:v>2963</x:v>
       </x:c>
       <x:c r="H8" s="17" t="n">
         <x:v>0.7918999999999999</x:v>
@@ -8641,10 +8733,12 @@
       <x:c r="E11" s="16" t="n">
         <x:v>7654.2</x:v>
       </x:c>
-      <x:c r="F11" s="16"/>
+      <x:c r="F11" s="16" t="n">
+        <x:v>9131</x:v>
+      </x:c>
       <x:c r="G11" s="16" t="n">
         <x:f>IFERROR(E11-F11,0)</x:f>
-        <x:v>7654.2</x:v>
+        <x:v>-1476.8000000000002</x:v>
       </x:c>
       <x:c r="H11" s="17" t="n">
         <x:v>0.6968000000000001</x:v>
@@ -8717,10 +8811,12 @@
       <x:c r="E13" s="16" t="n">
         <x:v>5099</x:v>
       </x:c>
-      <x:c r="F13" s="16"/>
+      <x:c r="F13" s="16" t="n">
+        <x:v>5199</x:v>
+      </x:c>
       <x:c r="G13" s="16" t="n">
         <x:f>IFERROR(E13-F13,0)</x:f>
-        <x:v>5099</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="H13" s="17" t="n">
         <x:v>0.7214</x:v>
@@ -8946,11 +9042,11 @@
         <x:v>9070</x:v>
       </x:c>
       <x:c r="F19" s="16" t="n">
-        <x:v>12510</x:v>
+        <x:v>12664</x:v>
       </x:c>
       <x:c r="G19" s="16" t="n">
         <x:f>IFERROR(E19-F19,0)</x:f>
-        <x:v>-3440</x:v>
+        <x:v>-3594</x:v>
       </x:c>
       <x:c r="H19" s="17" t="n">
         <x:v>0.7315</x:v>
@@ -8984,10 +9080,12 @@
       <x:c r="E20" s="16" t="n">
         <x:v>5409</x:v>
       </x:c>
-      <x:c r="F20" s="16"/>
+      <x:c r="F20" s="16" t="n">
+        <x:v>5395</x:v>
+      </x:c>
       <x:c r="G20" s="16" t="n">
         <x:f>IFERROR(E20-F20,0)</x:f>
-        <x:v>5409</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H20" s="17" t="n">
         <x:v>0.5212</x:v>
@@ -9021,10 +9119,12 @@
       <x:c r="E21" s="16" t="n">
         <x:v>5764</x:v>
       </x:c>
-      <x:c r="F21" s="16"/>
+      <x:c r="F21" s="16" t="n">
+        <x:v>2129</x:v>
+      </x:c>
       <x:c r="G21" s="16" t="n">
         <x:f>IFERROR(E21-F21,0)</x:f>
-        <x:v>5764</x:v>
+        <x:v>3635</x:v>
       </x:c>
       <x:c r="H21" s="17" t="n">
         <x:v>0.5703</x:v>
@@ -9136,10 +9236,12 @@
       <x:c r="E24" s="16" t="n">
         <x:v>3477</x:v>
       </x:c>
-      <x:c r="F24" s="16"/>
+      <x:c r="F24" s="16" t="n">
+        <x:v>1879</x:v>
+      </x:c>
       <x:c r="G24" s="16" t="n">
         <x:f>IFERROR(E24-F24,0)</x:f>
-        <x:v>3477</x:v>
+        <x:v>1598</x:v>
       </x:c>
       <x:c r="H24" s="17" t="n">
         <x:v>0.4439</x:v>
@@ -9212,10 +9314,12 @@
       <x:c r="E26" s="16" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="F26" s="16"/>
+      <x:c r="F26" s="16" t="n">
+        <x:v>5506</x:v>
+      </x:c>
       <x:c r="G26" s="16" t="n">
         <x:f>IFERROR(E26-F26,0)</x:f>
-        <x:v>3000</x:v>
+        <x:v>-2506</x:v>
       </x:c>
       <x:c r="H26" s="17" t="n">
         <x:v>0.14679999999999999</x:v>
@@ -9249,10 +9353,12 @@
       <x:c r="E27" s="16" t="n">
         <x:v>3554</x:v>
       </x:c>
-      <x:c r="F27" s="16"/>
+      <x:c r="F27" s="16" t="n">
+        <x:v>4558.2</x:v>
+      </x:c>
       <x:c r="G27" s="16" t="n">
         <x:f>IFERROR(E27-F27,0)</x:f>
-        <x:v>3554</x:v>
+        <x:v>-1004.1999999999998</x:v>
       </x:c>
       <x:c r="H27" s="17" t="n">
         <x:v>0.581</x:v>
@@ -9403,10 +9509,12 @@
       <x:c r="E31" s="16" t="n">
         <x:v>5485</x:v>
       </x:c>
-      <x:c r="F31" s="16"/>
+      <x:c r="F31" s="16" t="n">
+        <x:v>6139</x:v>
+      </x:c>
       <x:c r="G31" s="16" t="n">
         <x:f>IFERROR(E31-F31,0)</x:f>
-        <x:v>5485</x:v>
+        <x:v>-654</x:v>
       </x:c>
       <x:c r="H31" s="17" t="n">
         <x:v>0.7031999999999999</x:v>
@@ -9479,10 +9587,12 @@
       <x:c r="E33" s="16" t="n">
         <x:v>5207</x:v>
       </x:c>
-      <x:c r="F33" s="16"/>
+      <x:c r="F33" s="16" t="n">
+        <x:v>1555</x:v>
+      </x:c>
       <x:c r="G33" s="16" t="n">
         <x:f>IFERROR(E33-F33,0)</x:f>
-        <x:v>5207</x:v>
+        <x:v>3652</x:v>
       </x:c>
       <x:c r="H33" s="17" t="n">
         <x:v>0.4775</x:v>
@@ -9748,10 +9858,12 @@
       <x:c r="E40" s="16" t="n">
         <x:v>11526.75</x:v>
       </x:c>
-      <x:c r="F40" s="16"/>
+      <x:c r="F40" s="16" t="n">
+        <x:v>11015.9</x:v>
+      </x:c>
       <x:c r="G40" s="16" t="n">
         <x:f>IFERROR(E40-F40,0)</x:f>
-        <x:v>11526.75</x:v>
+        <x:v>510.85000000000036</x:v>
       </x:c>
       <x:c r="H40" s="17" t="n">
         <x:v>0.7736</x:v>
@@ -9824,10 +9936,12 @@
       <x:c r="E42" s="16" t="n">
         <x:v>3213.9</x:v>
       </x:c>
-      <x:c r="F42" s="16"/>
+      <x:c r="F42" s="16" t="n">
+        <x:v>6187</x:v>
+      </x:c>
       <x:c r="G42" s="16" t="n">
         <x:f>IFERROR(E42-F42,0)</x:f>
-        <x:v>3213.9</x:v>
+        <x:v>-2973.1</x:v>
       </x:c>
       <x:c r="H42" s="17" t="n">
         <x:v>0.45270000000000005</x:v>
@@ -9861,10 +9975,12 @@
       <x:c r="E43" s="16" t="n">
         <x:v>2473.2</x:v>
       </x:c>
-      <x:c r="F43" s="16"/>
+      <x:c r="F43" s="16" t="n">
+        <x:v>756</x:v>
+      </x:c>
       <x:c r="G43" s="16" t="n">
         <x:f>IFERROR(E43-F43,0)</x:f>
-        <x:v>2473.2</x:v>
+        <x:v>1717.1999999999998</x:v>
       </x:c>
       <x:c r="H43" s="17" t="n">
         <x:v>0.32049999999999995</x:v>
@@ -10015,10 +10131,12 @@
       <x:c r="E47" s="16" t="n">
         <x:v>4581</x:v>
       </x:c>
-      <x:c r="F47" s="16"/>
+      <x:c r="F47" s="16" t="n">
+        <x:v>2911</x:v>
+      </x:c>
       <x:c r="G47" s="16" t="n">
         <x:f>IFERROR(E47-F47,0)</x:f>
-        <x:v>4581</x:v>
+        <x:v>1670</x:v>
       </x:c>
       <x:c r="H47" s="17" t="n">
         <x:v>0.8521</x:v>
@@ -10053,11 +10171,11 @@
         <x:v>2494</x:v>
       </x:c>
       <x:c r="F48" s="16" t="n">
-        <x:v>4814</x:v>
+        <x:v>4615</x:v>
       </x:c>
       <x:c r="G48" s="16" t="n">
         <x:f>IFERROR(E48-F48,0)</x:f>
-        <x:v>-2320</x:v>
+        <x:v>-2121</x:v>
       </x:c>
       <x:c r="H48" s="17" t="n">
         <x:v>0.3563</x:v>
@@ -10092,11 +10210,11 @@
         <x:v>1660</x:v>
       </x:c>
       <x:c r="F49" s="16" t="n">
-        <x:v>6319</x:v>
+        <x:v>5835</x:v>
       </x:c>
       <x:c r="G49" s="16" t="n">
         <x:f>IFERROR(E49-F49,0)</x:f>
-        <x:v>-4659</x:v>
+        <x:v>-4175</x:v>
       </x:c>
       <x:c r="H49" s="17" t="n">
         <x:v>0.664</x:v>
@@ -10130,10 +10248,12 @@
       <x:c r="E50" s="16" t="n">
         <x:v>2226.1</x:v>
       </x:c>
-      <x:c r="F50" s="16"/>
+      <x:c r="F50" s="16" t="n">
+        <x:v>4214.15</x:v>
+      </x:c>
       <x:c r="G50" s="16" t="n">
         <x:f>IFERROR(E50-F50,0)</x:f>
-        <x:v>2226.1</x:v>
+        <x:v>-1988.0499999999997</x:v>
       </x:c>
       <x:c r="H50" s="17" t="n">
         <x:v>0.3153</x:v>
@@ -10206,10 +10326,12 @@
       <x:c r="E52" s="16" t="n">
         <x:v>2738</x:v>
       </x:c>
-      <x:c r="F52" s="16"/>
+      <x:c r="F52" s="16" t="n">
+        <x:v>3880</x:v>
+      </x:c>
       <x:c r="G52" s="16" t="n">
         <x:f>IFERROR(E52-F52,0)</x:f>
-        <x:v>2738</x:v>
+        <x:v>-1142</x:v>
       </x:c>
       <x:c r="H52" s="17" t="n">
         <x:v>0.6084</x:v>
@@ -10243,10 +10365,12 @@
       <x:c r="E53" s="16" t="n">
         <x:v>11207.05</x:v>
       </x:c>
-      <x:c r="F53" s="16"/>
+      <x:c r="F53" s="16" t="n">
+        <x:v>11152.2</x:v>
+      </x:c>
       <x:c r="G53" s="16" t="n">
         <x:f>IFERROR(E53-F53,0)</x:f>
-        <x:v>11207.05</x:v>
+        <x:v>54.849999999998545</x:v>
       </x:c>
       <x:c r="H53" s="17" t="n">
         <x:v>1.4009</x:v>
@@ -10319,10 +10443,12 @@
       <x:c r="E55" s="16" t="n">
         <x:v>4264</x:v>
       </x:c>
-      <x:c r="F55" s="16"/>
+      <x:c r="F55" s="16" t="n">
+        <x:v>3647</x:v>
+      </x:c>
       <x:c r="G55" s="16" t="n">
         <x:f>IFERROR(E55-F55,0)</x:f>
-        <x:v>4264</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="H55" s="17" t="n">
         <x:v>0.5134000000000001</x:v>
@@ -10430,10 +10556,12 @@
       <x:c r="E58" s="16" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="F58" s="16"/>
+      <x:c r="F58" s="16" t="n">
+        <x:v>2236</x:v>
+      </x:c>
       <x:c r="G58" s="16" t="n">
         <x:f>IFERROR(E58-F58,0)</x:f>
-        <x:v>2550</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="H58" s="17" t="n">
         <x:v>0.3333</x:v>
@@ -10543,10 +10671,12 @@
       <x:c r="E61" s="16" t="n">
         <x:v>1085</x:v>
       </x:c>
-      <x:c r="F61" s="16"/>
+      <x:c r="F61" s="16" t="n">
+        <x:v>484</x:v>
+      </x:c>
       <x:c r="G61" s="16" t="n">
         <x:f>IFERROR(E61-F61,0)</x:f>
-        <x:v>1085</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="H61" s="17" t="n">
         <x:v>0.2893</x:v>
@@ -10656,10 +10786,12 @@
       <x:c r="E64" s="16" t="n">
         <x:v>895</x:v>
       </x:c>
-      <x:c r="F64" s="16"/>
+      <x:c r="F64" s="16" t="n">
+        <x:v>1524</x:v>
+      </x:c>
       <x:c r="G64" s="16" t="n">
         <x:f>IFERROR(E64-F64,0)</x:f>
-        <x:v>895</x:v>
+        <x:v>-629</x:v>
       </x:c>
       <x:c r="H64" s="17" t="n">
         <x:v>0</x:v>
@@ -10793,7 +10925,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e805c7b3c674200"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f617b53d59d40b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
